--- a/StructureDefinition-onc-abc-chart.xlsx
+++ b/StructureDefinition-onc-abc-chart.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-03T01:44:04+00:00</t>
+    <t>2026-01-03T21:32:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-abc-chart.xlsx
+++ b/StructureDefinition-onc-abc-chart.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-03T21:32:36+00:00</t>
+    <t>2026-01-26T10:54:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-abc-chart.xlsx
+++ b/StructureDefinition-onc-abc-chart.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T10:54:48+00:00</t>
+    <t>2026-01-26T11:35:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-abc-chart.xlsx
+++ b/StructureDefinition-onc-abc-chart.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T11:35:16+00:00</t>
+    <t>2026-01-26T23:55:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-abc-chart.xlsx
+++ b/StructureDefinition-onc-abc-chart.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T23:55:12+00:00</t>
+    <t>2026-01-27T00:24:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-abc-chart.xlsx
+++ b/StructureDefinition-onc-abc-chart.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://fhir.clinyq.ai/StructureDefinition/onc-abc-chart</t>
+    <t>https://opennursingcoreig.com/StructureDefinition/onc-abc-chart</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-27T00:24:44+00:00</t>
+    <t>2026-01-27T01:09:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-abc-chart.xlsx
+++ b/StructureDefinition-onc-abc-chart.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-27T01:09:05+00:00</t>
+    <t>2026-01-27T08:26:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-abc-chart.xlsx
+++ b/StructureDefinition-onc-abc-chart.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-27T08:26:02+00:00</t>
+    <t>2026-01-27T09:30:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-abc-chart.xlsx
+++ b/StructureDefinition-onc-abc-chart.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-27T09:30:37+00:00</t>
+    <t>2026-06-29T21:13:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-abc-chart.xlsx
+++ b/StructureDefinition-onc-abc-chart.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T21:13:26+00:00</t>
+    <t>2026-07-04T08:39:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-abc-chart.xlsx
+++ b/StructureDefinition-onc-abc-chart.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-04T08:39:09+00:00</t>
+    <t>2026-07-04T09:17:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-abc-chart.xlsx
+++ b/StructureDefinition-onc-abc-chart.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-04T09:17:49+00:00</t>
+    <t>2026-07-09T21:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-abc-chart.xlsx
+++ b/StructureDefinition-onc-abc-chart.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T21:51:52+00:00</t>
+    <t>2026-07-09T22:02:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-abc-chart.xlsx
+++ b/StructureDefinition-onc-abc-chart.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T22:02:23+00:00</t>
+    <t>2026-07-09T22:05:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-abc-chart.xlsx
+++ b/StructureDefinition-onc-abc-chart.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T22:05:12+00:00</t>
+    <t>2026-07-09T22:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-abc-chart.xlsx
+++ b/StructureDefinition-onc-abc-chart.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T22:28:17+00:00</t>
+    <t>2026-07-10T11:01:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-abc-chart.xlsx
+++ b/StructureDefinition-onc-abc-chart.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T11:01:35+00:00</t>
+    <t>2026-07-11T09:35:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-abc-chart.xlsx
+++ b/StructureDefinition-onc-abc-chart.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4044" uniqueCount="569">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4044" uniqueCount="568">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T09:35:24+00:00</t>
+    <t>2026-07-11T09:46:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -617,14 +617,6 @@
   </si>
   <si>
     <t>Used for filtering what observations are retrieved and displayed.</t>
-  </si>
-  <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="http://terminology.hl7.org/CodeSystem/observation-category"/&gt;
-    &lt;code value="exam"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
     <t>Codes for high level observation categories.</t>
@@ -3922,7 +3914,7 @@
         <v>18</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>193</v>
+        <v>18</v>
       </c>
       <c r="T15" t="s" s="2">
         <v>18</v>
@@ -3940,23 +3932,23 @@
         <v>114</v>
       </c>
       <c r="Y15" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="Z15" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="Z15" t="s" s="2">
+      <c r="AA15" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB15" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AF15" t="s" s="2">
         <v>187</v>
@@ -3983,10 +3975,10 @@
         <v>18</v>
       </c>
       <c r="AN15" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AO15" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AO15" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>18</v>
@@ -3994,13 +3986,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B16" t="s" s="2">
         <v>187</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>18</v>
@@ -4044,7 +4036,7 @@
         <v>18</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>18</v>
@@ -4062,10 +4054,10 @@
         <v>114</v>
       </c>
       <c r="Y16" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="Z16" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>195</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>18</v>
@@ -4107,10 +4099,10 @@
         <v>18</v>
       </c>
       <c r="AN16" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AO16" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>18</v>
@@ -4118,14 +4110,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4147,16 +4139,16 @@
         <v>188</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>18</v>
@@ -4166,29 +4158,29 @@
         <v>18</v>
       </c>
       <c r="S17" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="T17" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U17" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V17" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W17" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X17" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="T17" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="U17" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="V17" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="W17" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="X17" t="s" s="2">
+      <c r="Y17" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="Y17" t="s" s="2">
+      <c r="Z17" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="Z17" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="AA17" t="s" s="2">
         <v>18</v>
       </c>
@@ -4205,7 +4197,7 @@
         <v>18</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>90</v>
@@ -4220,30 +4212,30 @@
         <v>102</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AL17" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="AL17" t="s" s="2">
+      <c r="AM17" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="AM17" t="s" s="2">
+      <c r="AN17" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AN17" t="s" s="2">
+      <c r="AO17" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="AO17" t="s" s="2">
+      <c r="AP17" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="AP17" t="s" s="2">
-        <v>218</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4266,19 +4258,19 @@
         <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="N18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>18</v>
@@ -4327,7 +4319,7 @@
         <v>18</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -4342,19 +4334,19 @@
         <v>102</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AL18" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM18" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="AL18" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM18" t="s" s="2">
+      <c r="AN18" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="AN18" t="s" s="2">
+      <c r="AO18" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>18</v>
@@ -4362,10 +4354,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4388,16 +4380,16 @@
         <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4447,7 +4439,7 @@
         <v>18</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -4468,13 +4460,13 @@
         <v>18</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>18</v>
@@ -4482,14 +4474,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4508,19 +4500,19 @@
         <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="N20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>18</v>
@@ -4569,7 +4561,7 @@
         <v>18</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4584,19 +4576,19 @@
         <v>102</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="AL20" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM20" t="s" s="2">
+      <c r="AN20" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="AN20" t="s" s="2">
+      <c r="AO20" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>18</v>
@@ -4604,14 +4596,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4630,19 +4622,19 @@
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="N21" t="s" s="2">
+      <c r="O21" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>18</v>
@@ -4691,7 +4683,7 @@
         <v>18</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4706,19 +4698,19 @@
         <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="AL21" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM21" t="s" s="2">
+      <c r="AN21" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="AN21" t="s" s="2">
+      <c r="AO21" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>18</v>
@@ -4726,10 +4718,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4752,16 +4744,16 @@
         <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4811,7 +4803,7 @@
         <v>18</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4832,13 +4824,13 @@
         <v>18</v>
       </c>
       <c r="AM22" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="AN22" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="AN22" t="s" s="2">
+      <c r="AO22" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>264</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>18</v>
@@ -4846,10 +4838,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4872,17 +4864,17 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>18</v>
@@ -4931,7 +4923,7 @@
         <v>18</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4946,19 +4938,19 @@
         <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="AL23" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AN23" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="AN23" t="s" s="2">
+      <c r="AO23" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>18</v>
@@ -4966,10 +4958,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4995,16 +4987,16 @@
         <v>188</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="N24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>18</v>
@@ -5033,7 +5025,7 @@
       </c>
       <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>18</v>
@@ -5051,7 +5043,7 @@
         <v>18</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -5060,7 +5052,7 @@
         <v>90</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>102</v>
@@ -5069,27 +5061,27 @@
         <v>18</v>
       </c>
       <c r="AL24" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="AM24" t="s" s="2">
+      <c r="AN24" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AN24" t="s" s="2">
+      <c r="AO24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP24" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP24" t="s" s="2">
-        <v>284</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5115,16 +5107,16 @@
         <v>188</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="N25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>18</v>
@@ -5149,14 +5141,14 @@
         <v>18</v>
       </c>
       <c r="X25" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="Y25" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="Y25" t="s" s="2">
+      <c r="Z25" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="Z25" t="s" s="2">
-        <v>292</v>
-      </c>
       <c r="AA25" t="s" s="2">
         <v>18</v>
       </c>
@@ -5173,7 +5165,7 @@
         <v>18</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -5182,7 +5174,7 @@
         <v>90</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>102</v>
@@ -5197,7 +5189,7 @@
         <v>133</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>18</v>
@@ -5208,14 +5200,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -5237,16 +5229,16 @@
         <v>188</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="N26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>18</v>
@@ -5271,14 +5263,14 @@
         <v>18</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Y26" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="Z26" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="Z26" t="s" s="2">
-        <v>302</v>
-      </c>
       <c r="AA26" t="s" s="2">
         <v>18</v>
       </c>
@@ -5295,7 +5287,7 @@
         <v>18</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -5313,27 +5305,27 @@
         <v>18</v>
       </c>
       <c r="AL26" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AM26" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="AM26" t="s" s="2">
+      <c r="AN26" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="AN26" t="s" s="2">
+      <c r="AO26" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP26" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP26" t="s" s="2">
-        <v>306</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5356,19 +5348,19 @@
         <v>18</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>18</v>
@@ -5417,7 +5409,7 @@
         <v>18</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -5438,10 +5430,10 @@
         <v>18</v>
       </c>
       <c r="AM27" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>18</v>
@@ -5452,10 +5444,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5481,13 +5473,13 @@
         <v>188</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5513,14 +5505,14 @@
         <v>18</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Y28" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="Z28" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="Z28" t="s" s="2">
-        <v>320</v>
-      </c>
       <c r="AA28" t="s" s="2">
         <v>18</v>
       </c>
@@ -5537,7 +5529,7 @@
         <v>18</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5555,27 +5547,27 @@
         <v>18</v>
       </c>
       <c r="AL28" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AM28" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="AM28" t="s" s="2">
+      <c r="AN28" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="AN28" t="s" s="2">
+      <c r="AO28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP28" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP28" t="s" s="2">
-        <v>324</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5601,16 +5593,16 @@
         <v>188</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="N29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>18</v>
@@ -5635,14 +5627,14 @@
         <v>18</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Y29" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="Z29" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="Z29" t="s" s="2">
-        <v>331</v>
-      </c>
       <c r="AA29" t="s" s="2">
         <v>18</v>
       </c>
@@ -5659,7 +5651,7 @@
         <v>18</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5680,10 +5672,10 @@
         <v>18</v>
       </c>
       <c r="AM29" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>18</v>
@@ -5694,10 +5686,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5720,16 +5712,16 @@
         <v>18</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>338</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5779,7 +5771,7 @@
         <v>18</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5797,27 +5789,27 @@
         <v>18</v>
       </c>
       <c r="AL30" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="AM30" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="AM30" t="s" s="2">
+      <c r="AN30" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="AN30" t="s" s="2">
+      <c r="AO30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP30" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP30" t="s" s="2">
-        <v>342</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5840,16 +5832,16 @@
         <v>18</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5899,7 +5891,7 @@
         <v>18</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5917,27 +5909,27 @@
         <v>18</v>
       </c>
       <c r="AL31" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AM31" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="AM31" t="s" s="2">
+      <c r="AN31" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="AN31" t="s" s="2">
+      <c r="AO31" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP31" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP31" t="s" s="2">
-        <v>351</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5960,19 +5952,19 @@
         <v>18</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="N32" t="s" s="2">
+      <c r="O32" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>18</v>
@@ -6021,7 +6013,7 @@
         <v>18</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -6033,19 +6025,19 @@
         <v>18</v>
       </c>
       <c r="AJ32" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM32" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="AK32" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM32" t="s" s="2">
+      <c r="AN32" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>18</v>
@@ -6056,10 +6048,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6082,13 +6074,13 @@
         <v>18</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6139,7 +6131,7 @@
         <v>18</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -6163,7 +6155,7 @@
         <v>18</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>18</v>
@@ -6174,10 +6166,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6206,7 +6198,7 @@
         <v>137</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>139</v>
@@ -6259,7 +6251,7 @@
         <v>18</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -6283,7 +6275,7 @@
         <v>18</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>18</v>
@@ -6294,14 +6286,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6323,10 +6315,10 @@
         <v>136</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="N35" t="s" s="2">
         <v>139</v>
@@ -6381,7 +6373,7 @@
         <v>18</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -6416,10 +6408,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6442,13 +6434,13 @@
         <v>18</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6499,7 +6491,7 @@
         <v>18</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6508,7 +6500,7 @@
         <v>90</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>102</v>
@@ -6520,10 +6512,10 @@
         <v>18</v>
       </c>
       <c r="AM36" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>18</v>
@@ -6534,10 +6526,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6560,13 +6552,13 @@
         <v>18</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6617,7 +6609,7 @@
         <v>18</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6626,7 +6618,7 @@
         <v>90</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>102</v>
@@ -6638,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>18</v>
@@ -6652,10 +6644,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6681,16 +6673,16 @@
         <v>188</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="N38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>18</v>
@@ -6718,11 +6710,11 @@
         <v>114</v>
       </c>
       <c r="Y38" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="Z38" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="Z38" t="s" s="2">
-        <v>392</v>
-      </c>
       <c r="AA38" t="s" s="2">
         <v>18</v>
       </c>
@@ -6739,7 +6731,7 @@
         <v>18</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6757,13 +6749,13 @@
         <v>18</v>
       </c>
       <c r="AL38" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="AM38" t="s" s="2">
-        <v>394</v>
-      </c>
       <c r="AN38" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>18</v>
@@ -6774,10 +6766,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6803,16 +6795,16 @@
         <v>188</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>18</v>
@@ -6837,14 +6829,14 @@
         <v>18</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Y39" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="Z39" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="Z39" t="s" s="2">
-        <v>401</v>
-      </c>
       <c r="AA39" t="s" s="2">
         <v>18</v>
       </c>
@@ -6861,7 +6853,7 @@
         <v>18</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6879,13 +6871,13 @@
         <v>18</v>
       </c>
       <c r="AL39" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AM39" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="AM39" t="s" s="2">
-        <v>394</v>
-      </c>
       <c r="AN39" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>18</v>
@@ -6896,10 +6888,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6922,17 +6914,17 @@
         <v>18</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>18</v>
@@ -6981,7 +6973,7 @@
         <v>18</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -7005,7 +6997,7 @@
         <v>18</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>18</v>
@@ -7016,10 +7008,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7042,13 +7034,13 @@
         <v>18</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7099,7 +7091,7 @@
         <v>18</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -7120,10 +7112,10 @@
         <v>18</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>18</v>
@@ -7134,10 +7126,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7160,16 +7152,16 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7219,7 +7211,7 @@
         <v>18</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -7240,10 +7232,10 @@
         <v>18</v>
       </c>
       <c r="AM42" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AN42" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>18</v>
@@ -7254,10 +7246,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7280,16 +7272,16 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7339,7 +7331,7 @@
         <v>18</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -7360,10 +7352,10 @@
         <v>18</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>18</v>
@@ -7374,10 +7366,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7385,7 +7377,7 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>79</v>
@@ -7400,19 +7392,19 @@
         <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="N44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>18</v>
@@ -7449,17 +7441,17 @@
         <v>18</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AC44" s="2"/>
       <c r="AD44" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7480,10 +7472,10 @@
         <v>18</v>
       </c>
       <c r="AM44" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>18</v>
@@ -7494,10 +7486,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7520,13 +7512,13 @@
         <v>18</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7577,7 +7569,7 @@
         <v>18</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7601,7 +7593,7 @@
         <v>18</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>18</v>
@@ -7612,10 +7604,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7644,7 +7636,7 @@
         <v>137</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>139</v>
@@ -7697,7 +7689,7 @@
         <v>18</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7721,7 +7713,7 @@
         <v>18</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>18</v>
@@ -7732,14 +7724,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7761,10 +7753,10 @@
         <v>136</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>139</v>
@@ -7819,7 +7811,7 @@
         <v>18</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7854,10 +7846,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7883,16 +7875,16 @@
         <v>188</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="N48" t="s" s="2">
-        <v>440</v>
-      </c>
       <c r="O48" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>18</v>
@@ -7917,14 +7909,14 @@
         <v>18</v>
       </c>
       <c r="X48" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="Y48" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="Y48" t="s" s="2">
+      <c r="Z48" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="Z48" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="AA48" t="s" s="2">
         <v>18</v>
       </c>
@@ -7941,7 +7933,7 @@
         <v>18</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>90</v>
@@ -7959,16 +7951,16 @@
         <v>18</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AM48" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AN48" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AN48" t="s" s="2">
+      <c r="AO48" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>18</v>
@@ -7976,10 +7968,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8002,19 +7994,19 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="N49" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="M49" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>445</v>
-      </c>
       <c r="O49" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>18</v>
@@ -8063,7 +8055,7 @@
         <v>18</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -8081,27 +8073,27 @@
         <v>18</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AM49" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AN49" t="s" s="2">
+      <c r="AO49" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP49" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP49" t="s" s="2">
-        <v>284</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8127,16 +8119,16 @@
         <v>188</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="N50" t="s" s="2">
-        <v>450</v>
-      </c>
       <c r="O50" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>18</v>
@@ -8161,14 +8153,14 @@
         <v>18</v>
       </c>
       <c r="X50" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="Y50" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="Y50" t="s" s="2">
+      <c r="Z50" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="Z50" t="s" s="2">
-        <v>292</v>
-      </c>
       <c r="AA50" t="s" s="2">
         <v>18</v>
       </c>
@@ -8185,7 +8177,7 @@
         <v>18</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -8194,7 +8186,7 @@
         <v>90</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>102</v>
@@ -8209,7 +8201,7 @@
         <v>133</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>18</v>
@@ -8220,14 +8212,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8249,16 +8241,16 @@
         <v>188</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="N51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>18</v>
@@ -8283,14 +8275,14 @@
         <v>18</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Y51" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="Z51" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="Z51" t="s" s="2">
-        <v>302</v>
-      </c>
       <c r="AA51" t="s" s="2">
         <v>18</v>
       </c>
@@ -8307,7 +8299,7 @@
         <v>18</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -8325,27 +8317,27 @@
         <v>18</v>
       </c>
       <c r="AL51" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AM51" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="AM51" t="s" s="2">
+      <c r="AN51" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="AN51" t="s" s="2">
+      <c r="AO51" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP51" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP51" t="s" s="2">
-        <v>306</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8371,16 +8363,16 @@
         <v>80</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="M52" t="s" s="2">
-        <v>454</v>
-      </c>
       <c r="N52" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="O52" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>18</v>
@@ -8429,7 +8421,7 @@
         <v>18</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8450,10 +8442,10 @@
         <v>18</v>
       </c>
       <c r="AM52" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AN52" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>18</v>
@@ -8464,13 +8456,13 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="C53" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="C53" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="D53" t="s" s="2">
         <v>18</v>
@@ -8492,19 +8484,19 @@
         <v>91</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="N53" t="s" s="2">
+      <c r="O53" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>18</v>
@@ -8553,7 +8545,7 @@
         <v>18</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8574,10 +8566,10 @@
         <v>18</v>
       </c>
       <c r="AM53" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AN53" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>18</v>
@@ -8588,10 +8580,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8614,13 +8606,13 @@
         <v>18</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8671,7 +8663,7 @@
         <v>18</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8695,7 +8687,7 @@
         <v>18</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>18</v>
@@ -8706,10 +8698,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8738,7 +8730,7 @@
         <v>137</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>139</v>
@@ -8791,7 +8783,7 @@
         <v>18</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8815,7 +8807,7 @@
         <v>18</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>18</v>
@@ -8826,14 +8818,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8855,10 +8847,10 @@
         <v>136</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="N56" t="s" s="2">
         <v>139</v>
@@ -8913,7 +8905,7 @@
         <v>18</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8948,10 +8940,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8977,16 +8969,16 @@
         <v>188</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="N57" t="s" s="2">
-        <v>440</v>
-      </c>
       <c r="O57" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>18</v>
@@ -8996,7 +8988,7 @@
         <v>18</v>
       </c>
       <c r="S57" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="T57" t="s" s="2">
         <v>18</v>
@@ -9011,14 +9003,14 @@
         <v>18</v>
       </c>
       <c r="X57" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="Y57" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="Y57" t="s" s="2">
+      <c r="Z57" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="Z57" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="AA57" t="s" s="2">
         <v>18</v>
       </c>
@@ -9035,7 +9027,7 @@
         <v>18</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>90</v>
@@ -9053,16 +9045,16 @@
         <v>18</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AM57" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AN57" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AN57" t="s" s="2">
+      <c r="AO57" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>18</v>
@@ -9070,10 +9062,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9096,19 +9088,19 @@
         <v>91</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>18</v>
@@ -9157,7 +9149,7 @@
         <v>18</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -9175,27 +9167,27 @@
         <v>18</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AM58" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AN58" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AN58" t="s" s="2">
+      <c r="AO58" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP58" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP58" t="s" s="2">
-        <v>284</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9221,16 +9213,16 @@
         <v>188</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="N59" t="s" s="2">
-        <v>450</v>
-      </c>
       <c r="O59" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>18</v>
@@ -9255,14 +9247,14 @@
         <v>18</v>
       </c>
       <c r="X59" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="Y59" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="Y59" t="s" s="2">
+      <c r="Z59" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="Z59" t="s" s="2">
-        <v>292</v>
-      </c>
       <c r="AA59" t="s" s="2">
         <v>18</v>
       </c>
@@ -9279,7 +9271,7 @@
         <v>18</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -9288,7 +9280,7 @@
         <v>90</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>102</v>
@@ -9303,7 +9295,7 @@
         <v>133</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>18</v>
@@ -9314,14 +9306,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9343,16 +9335,16 @@
         <v>188</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="N60" t="s" s="2">
+      <c r="O60" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>18</v>
@@ -9377,14 +9369,14 @@
         <v>18</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Y60" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="Z60" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="Z60" t="s" s="2">
-        <v>302</v>
-      </c>
       <c r="AA60" t="s" s="2">
         <v>18</v>
       </c>
@@ -9401,7 +9393,7 @@
         <v>18</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -9419,27 +9411,27 @@
         <v>18</v>
       </c>
       <c r="AL60" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AM60" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="AM60" t="s" s="2">
+      <c r="AN60" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="AN60" t="s" s="2">
+      <c r="AO60" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP60" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP60" t="s" s="2">
-        <v>306</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9465,16 +9457,16 @@
         <v>80</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="M61" t="s" s="2">
-        <v>454</v>
-      </c>
       <c r="N61" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="O61" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>18</v>
@@ -9523,7 +9515,7 @@
         <v>18</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -9544,10 +9536,10 @@
         <v>18</v>
       </c>
       <c r="AM61" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AN61" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>18</v>
@@ -9558,13 +9550,13 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="C62" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="C62" t="s" s="2">
-        <v>468</v>
       </c>
       <c r="D62" t="s" s="2">
         <v>18</v>
@@ -9586,19 +9578,19 @@
         <v>91</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="N62" t="s" s="2">
+      <c r="O62" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>18</v>
@@ -9647,7 +9639,7 @@
         <v>18</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9668,10 +9660,10 @@
         <v>18</v>
       </c>
       <c r="AM62" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AN62" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>18</v>
@@ -9682,10 +9674,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9708,13 +9700,13 @@
         <v>18</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9765,7 +9757,7 @@
         <v>18</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9789,7 +9781,7 @@
         <v>18</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>18</v>
@@ -9800,10 +9792,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9832,7 +9824,7 @@
         <v>137</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="N64" t="s" s="2">
         <v>139</v>
@@ -9885,7 +9877,7 @@
         <v>18</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9909,7 +9901,7 @@
         <v>18</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>18</v>
@@ -9920,14 +9912,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9949,10 +9941,10 @@
         <v>136</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="N65" t="s" s="2">
         <v>139</v>
@@ -10007,7 +9999,7 @@
         <v>18</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -10042,10 +10034,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10071,16 +10063,16 @@
         <v>188</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="N66" t="s" s="2">
-        <v>440</v>
-      </c>
       <c r="O66" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>18</v>
@@ -10090,7 +10082,7 @@
         <v>18</v>
       </c>
       <c r="S66" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="T66" t="s" s="2">
         <v>18</v>
@@ -10105,14 +10097,14 @@
         <v>18</v>
       </c>
       <c r="X66" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="Y66" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="Y66" t="s" s="2">
+      <c r="Z66" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="Z66" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="AA66" t="s" s="2">
         <v>18</v>
       </c>
@@ -10129,7 +10121,7 @@
         <v>18</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>90</v>
@@ -10147,16 +10139,16 @@
         <v>18</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AM66" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AN66" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AN66" t="s" s="2">
+      <c r="AO66" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>18</v>
@@ -10164,10 +10156,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10190,19 +10182,19 @@
         <v>91</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>18</v>
@@ -10251,7 +10243,7 @@
         <v>18</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -10269,27 +10261,27 @@
         <v>18</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AM67" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AN67" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AN67" t="s" s="2">
+      <c r="AO67" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP67" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP67" t="s" s="2">
-        <v>284</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10315,16 +10307,16 @@
         <v>188</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="N68" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="N68" t="s" s="2">
-        <v>450</v>
-      </c>
       <c r="O68" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>18</v>
@@ -10349,14 +10341,14 @@
         <v>18</v>
       </c>
       <c r="X68" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="Y68" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="Y68" t="s" s="2">
+      <c r="Z68" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="Z68" t="s" s="2">
-        <v>292</v>
-      </c>
       <c r="AA68" t="s" s="2">
         <v>18</v>
       </c>
@@ -10373,7 +10365,7 @@
         <v>18</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -10382,7 +10374,7 @@
         <v>90</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>102</v>
@@ -10397,7 +10389,7 @@
         <v>133</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>18</v>
@@ -10408,14 +10400,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -10437,16 +10429,16 @@
         <v>188</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="N69" t="s" s="2">
+      <c r="O69" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>18</v>
@@ -10471,14 +10463,14 @@
         <v>18</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Y69" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="Z69" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="Z69" t="s" s="2">
-        <v>302</v>
-      </c>
       <c r="AA69" t="s" s="2">
         <v>18</v>
       </c>
@@ -10495,7 +10487,7 @@
         <v>18</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10513,27 +10505,27 @@
         <v>18</v>
       </c>
       <c r="AL69" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AM69" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="AM69" t="s" s="2">
+      <c r="AN69" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="AN69" t="s" s="2">
+      <c r="AO69" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP69" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP69" t="s" s="2">
-        <v>306</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10559,16 +10551,16 @@
         <v>80</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="M70" t="s" s="2">
-        <v>454</v>
-      </c>
       <c r="N70" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="O70" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>18</v>
@@ -10617,7 +10609,7 @@
         <v>18</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10638,10 +10630,10 @@
         <v>18</v>
       </c>
       <c r="AM70" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AN70" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>18</v>
@@ -10652,13 +10644,13 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="C71" t="s" s="2">
         <v>479</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="C71" t="s" s="2">
-        <v>480</v>
       </c>
       <c r="D71" t="s" s="2">
         <v>18</v>
@@ -10680,19 +10672,19 @@
         <v>91</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="N71" t="s" s="2">
+      <c r="O71" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>18</v>
@@ -10741,7 +10733,7 @@
         <v>18</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10762,10 +10754,10 @@
         <v>18</v>
       </c>
       <c r="AM71" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AN71" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>18</v>
@@ -10776,10 +10768,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10802,13 +10794,13 @@
         <v>18</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="L72" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="L72" t="s" s="2">
+      <c r="M72" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10859,7 +10851,7 @@
         <v>18</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10883,7 +10875,7 @@
         <v>18</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>18</v>
@@ -10894,10 +10886,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10926,7 +10918,7 @@
         <v>137</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="N73" t="s" s="2">
         <v>139</v>
@@ -10979,7 +10971,7 @@
         <v>18</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -11003,7 +10995,7 @@
         <v>18</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>18</v>
@@ -11014,14 +11006,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -11043,10 +11035,10 @@
         <v>136</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>139</v>
@@ -11101,7 +11093,7 @@
         <v>18</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -11136,10 +11128,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11165,16 +11157,16 @@
         <v>188</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="N75" t="s" s="2">
-        <v>440</v>
-      </c>
       <c r="O75" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>18</v>
@@ -11184,7 +11176,7 @@
         <v>18</v>
       </c>
       <c r="S75" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="T75" t="s" s="2">
         <v>18</v>
@@ -11199,14 +11191,14 @@
         <v>18</v>
       </c>
       <c r="X75" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="Y75" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="Y75" t="s" s="2">
+      <c r="Z75" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="Z75" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="AA75" t="s" s="2">
         <v>18</v>
       </c>
@@ -11223,7 +11215,7 @@
         <v>18</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>90</v>
@@ -11241,16 +11233,16 @@
         <v>18</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AM75" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AN75" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AN75" t="s" s="2">
+      <c r="AO75" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AO75" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>18</v>
@@ -11258,10 +11250,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11284,19 +11276,19 @@
         <v>91</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>18</v>
@@ -11345,7 +11337,7 @@
         <v>18</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -11363,27 +11355,27 @@
         <v>18</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AM76" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AN76" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AN76" t="s" s="2">
+      <c r="AO76" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP76" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP76" t="s" s="2">
-        <v>284</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11409,16 +11401,16 @@
         <v>188</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="M77" t="s" s="2">
+      <c r="N77" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="N77" t="s" s="2">
-        <v>450</v>
-      </c>
       <c r="O77" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>18</v>
@@ -11443,14 +11435,14 @@
         <v>18</v>
       </c>
       <c r="X77" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="Y77" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="Y77" t="s" s="2">
+      <c r="Z77" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="Z77" t="s" s="2">
-        <v>292</v>
-      </c>
       <c r="AA77" t="s" s="2">
         <v>18</v>
       </c>
@@ -11467,7 +11459,7 @@
         <v>18</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -11476,7 +11468,7 @@
         <v>90</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>102</v>
@@ -11491,7 +11483,7 @@
         <v>133</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>18</v>
@@ -11502,14 +11494,14 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -11531,16 +11523,16 @@
         <v>188</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="N78" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="N78" t="s" s="2">
+      <c r="O78" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>18</v>
@@ -11565,14 +11557,14 @@
         <v>18</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Y78" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="Z78" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="Z78" t="s" s="2">
-        <v>302</v>
-      </c>
       <c r="AA78" t="s" s="2">
         <v>18</v>
       </c>
@@ -11589,7 +11581,7 @@
         <v>18</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11607,27 +11599,27 @@
         <v>18</v>
       </c>
       <c r="AL78" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AM78" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="AM78" t="s" s="2">
+      <c r="AN78" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="AN78" t="s" s="2">
+      <c r="AO78" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP78" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="AO78" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP78" t="s" s="2">
-        <v>306</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11653,16 +11645,16 @@
         <v>80</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="M79" t="s" s="2">
-        <v>454</v>
-      </c>
       <c r="N79" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="O79" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>18</v>
@@ -11711,7 +11703,7 @@
         <v>18</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11732,10 +11724,10 @@
         <v>18</v>
       </c>
       <c r="AM79" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AN79" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="AN79" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>18</v>
@@ -11746,13 +11738,13 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="C80" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="B80" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="C80" t="s" s="2">
-        <v>492</v>
       </c>
       <c r="D80" t="s" s="2">
         <v>18</v>
@@ -11774,19 +11766,19 @@
         <v>91</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="M80" t="s" s="2">
+      <c r="N80" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="N80" t="s" s="2">
+      <c r="O80" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>18</v>
@@ -11835,7 +11827,7 @@
         <v>18</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -11856,10 +11848,10 @@
         <v>18</v>
       </c>
       <c r="AM80" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AN80" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>18</v>
@@ -11870,10 +11862,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11896,13 +11888,13 @@
         <v>18</v>
       </c>
       <c r="K81" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="L81" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="L81" t="s" s="2">
+      <c r="M81" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11953,7 +11945,7 @@
         <v>18</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -11977,7 +11969,7 @@
         <v>18</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>18</v>
@@ -11988,10 +11980,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12020,7 +12012,7 @@
         <v>137</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="N82" t="s" s="2">
         <v>139</v>
@@ -12073,7 +12065,7 @@
         <v>18</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -12097,7 +12089,7 @@
         <v>18</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>18</v>
@@ -12108,14 +12100,14 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -12137,10 +12129,10 @@
         <v>136</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>139</v>
@@ -12195,7 +12187,7 @@
         <v>18</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -12230,10 +12222,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12259,16 +12251,16 @@
         <v>188</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="N84" t="s" s="2">
-        <v>440</v>
-      </c>
       <c r="O84" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>18</v>
@@ -12278,7 +12270,7 @@
         <v>18</v>
       </c>
       <c r="S84" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="T84" t="s" s="2">
         <v>18</v>
@@ -12293,14 +12285,14 @@
         <v>18</v>
       </c>
       <c r="X84" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="Y84" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="Y84" t="s" s="2">
+      <c r="Z84" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="Z84" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="AA84" t="s" s="2">
         <v>18</v>
       </c>
@@ -12317,7 +12309,7 @@
         <v>18</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>90</v>
@@ -12335,16 +12327,16 @@
         <v>18</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AM84" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AN84" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AN84" t="s" s="2">
+      <c r="AO84" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AO84" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>18</v>
@@ -12352,10 +12344,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12378,19 +12370,19 @@
         <v>91</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="N85" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="M85" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>445</v>
-      </c>
       <c r="O85" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>18</v>
@@ -12439,7 +12431,7 @@
         <v>18</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -12457,27 +12449,27 @@
         <v>18</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AM85" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AN85" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AN85" t="s" s="2">
+      <c r="AO85" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP85" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AO85" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP85" t="s" s="2">
-        <v>284</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="B86" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="B86" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12500,13 +12492,13 @@
         <v>18</v>
       </c>
       <c r="K86" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="L86" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="L86" t="s" s="2">
+      <c r="M86" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12557,7 +12549,7 @@
         <v>18</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -12581,7 +12573,7 @@
         <v>18</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>18</v>
@@ -12592,10 +12584,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="B87" t="s" s="2">
         <v>502</v>
-      </c>
-      <c r="B87" t="s" s="2">
-        <v>503</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12624,7 +12616,7 @@
         <v>137</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="N87" t="s" s="2">
         <v>139</v>
@@ -12665,19 +12657,19 @@
         <v>18</v>
       </c>
       <c r="AB87" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AC87" t="s" s="2">
         <v>504</v>
       </c>
-      <c r="AC87" t="s" s="2">
-        <v>505</v>
-      </c>
       <c r="AD87" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -12701,7 +12693,7 @@
         <v>18</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>18</v>
@@ -12712,10 +12704,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="B88" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="B88" t="s" s="2">
-        <v>507</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12738,19 +12730,19 @@
         <v>91</v>
       </c>
       <c r="K88" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="L88" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="L88" t="s" s="2">
+      <c r="M88" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="M88" t="s" s="2">
+      <c r="N88" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="N88" t="s" s="2">
+      <c r="O88" t="s" s="2">
         <v>511</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>512</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>18</v>
@@ -12799,7 +12791,7 @@
         <v>18</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -12820,10 +12812,10 @@
         <v>18</v>
       </c>
       <c r="AM88" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="AN88" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>515</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>18</v>
@@ -12834,10 +12826,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="B89" t="s" s="2">
         <v>516</v>
-      </c>
-      <c r="B89" t="s" s="2">
-        <v>517</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12863,20 +12855,20 @@
         <v>110</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="M89" t="s" s="2">
         <v>518</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>519</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="P89" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Q89" t="s" s="2">
         <v>520</v>
-      </c>
-      <c r="P89" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Q89" t="s" s="2">
-        <v>521</v>
       </c>
       <c r="R89" t="s" s="2">
         <v>18</v>
@@ -12900,28 +12892,28 @@
         <v>179</v>
       </c>
       <c r="Y89" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="Z89" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="Z89" t="s" s="2">
+      <c r="AA89" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF89" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="AA89" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB89" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC89" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD89" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE89" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF89" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -12942,10 +12934,10 @@
         <v>18</v>
       </c>
       <c r="AM89" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AN89" t="s" s="2">
         <v>525</v>
-      </c>
-      <c r="AN89" t="s" s="2">
-        <v>526</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>18</v>
@@ -12956,10 +12948,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="B90" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="B90" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12982,17 +12974,17 @@
         <v>91</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>529</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>530</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>18</v>
@@ -13002,46 +12994,46 @@
         <v>18</v>
       </c>
       <c r="S90" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF90" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="T90" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="U90" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="V90" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="W90" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="X90" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Y90" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Z90" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AA90" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB90" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC90" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD90" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE90" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF90" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -13062,10 +13054,10 @@
         <v>18</v>
       </c>
       <c r="AM90" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="AN90" t="s" s="2">
         <v>534</v>
-      </c>
-      <c r="AN90" t="s" s="2">
-        <v>535</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>18</v>
@@ -13076,10 +13068,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="B91" t="s" s="2">
         <v>536</v>
-      </c>
-      <c r="B91" t="s" s="2">
-        <v>537</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13105,14 +13097,14 @@
         <v>104</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="M91" t="s" s="2">
-        <v>539</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>18</v>
@@ -13122,46 +13114,46 @@
         <v>18</v>
       </c>
       <c r="S91" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF91" t="s" s="2">
         <v>541</v>
-      </c>
-      <c r="T91" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="U91" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="V91" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="W91" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="X91" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Y91" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Z91" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AA91" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB91" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC91" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD91" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE91" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF91" t="s" s="2">
-        <v>542</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -13170,7 +13162,7 @@
         <v>90</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>102</v>
@@ -13182,10 +13174,10 @@
         <v>18</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>18</v>
@@ -13196,10 +13188,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="B92" t="s" s="2">
         <v>545</v>
-      </c>
-      <c r="B92" t="s" s="2">
-        <v>546</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13225,16 +13217,16 @@
         <v>110</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>547</v>
       </c>
-      <c r="M92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>548</v>
       </c>
-      <c r="N92" t="s" s="2">
+      <c r="O92" t="s" s="2">
         <v>549</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>550</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>18</v>
@@ -13244,7 +13236,7 @@
         <v>18</v>
       </c>
       <c r="S92" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="T92" t="s" s="2">
         <v>18</v>
@@ -13283,7 +13275,7 @@
         <v>18</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -13304,10 +13296,10 @@
         <v>18</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>18</v>
@@ -13318,10 +13310,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13347,16 +13339,16 @@
         <v>188</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="M93" t="s" s="2">
+      <c r="N93" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="N93" t="s" s="2">
-        <v>450</v>
-      </c>
       <c r="O93" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>18</v>
@@ -13381,14 +13373,14 @@
         <v>18</v>
       </c>
       <c r="X93" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="Y93" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="Y93" t="s" s="2">
+      <c r="Z93" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="Z93" t="s" s="2">
-        <v>292</v>
-      </c>
       <c r="AA93" t="s" s="2">
         <v>18</v>
       </c>
@@ -13405,7 +13397,7 @@
         <v>18</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -13414,7 +13406,7 @@
         <v>90</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AJ93" t="s" s="2">
         <v>102</v>
@@ -13429,7 +13421,7 @@
         <v>133</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>18</v>
@@ -13440,14 +13432,14 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -13469,16 +13461,16 @@
         <v>188</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="N94" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="N94" t="s" s="2">
+      <c r="O94" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>18</v>
@@ -13503,14 +13495,14 @@
         <v>18</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Y94" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="Z94" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="Z94" t="s" s="2">
-        <v>302</v>
-      </c>
       <c r="AA94" t="s" s="2">
         <v>18</v>
       </c>
@@ -13527,7 +13519,7 @@
         <v>18</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -13545,27 +13537,27 @@
         <v>18</v>
       </c>
       <c r="AL94" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AM94" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="AM94" t="s" s="2">
+      <c r="AN94" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="AN94" t="s" s="2">
+      <c r="AO94" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP94" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="AO94" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP94" t="s" s="2">
-        <v>306</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13591,16 +13583,16 @@
         <v>80</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="M95" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="M95" t="s" s="2">
-        <v>454</v>
-      </c>
       <c r="N95" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="O95" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>18</v>
@@ -13649,7 +13641,7 @@
         <v>18</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -13670,10 +13662,10 @@
         <v>18</v>
       </c>
       <c r="AM95" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AN95" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="AN95" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>18</v>
@@ -13684,13 +13676,13 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="C96" t="s" s="2">
         <v>556</v>
-      </c>
-      <c r="B96" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="C96" t="s" s="2">
-        <v>557</v>
       </c>
       <c r="D96" t="s" s="2">
         <v>18</v>
@@ -13712,19 +13704,19 @@
         <v>91</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="M96" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="M96" t="s" s="2">
+      <c r="N96" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="N96" t="s" s="2">
+      <c r="O96" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>18</v>
@@ -13773,7 +13765,7 @@
         <v>18</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -13794,10 +13786,10 @@
         <v>18</v>
       </c>
       <c r="AM96" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AN96" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="AN96" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>18</v>
@@ -13808,10 +13800,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13834,13 +13826,13 @@
         <v>18</v>
       </c>
       <c r="K97" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="L97" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="L97" t="s" s="2">
+      <c r="M97" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -13891,7 +13883,7 @@
         <v>18</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
@@ -13915,7 +13907,7 @@
         <v>18</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>18</v>
@@ -13926,10 +13918,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13958,7 +13950,7 @@
         <v>137</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="N98" t="s" s="2">
         <v>139</v>
@@ -14011,7 +14003,7 @@
         <v>18</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>78</v>
@@ -14035,7 +14027,7 @@
         <v>18</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>18</v>
@@ -14046,14 +14038,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -14075,10 +14067,10 @@
         <v>136</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="M99" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>139</v>
@@ -14133,7 +14125,7 @@
         <v>18</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
@@ -14168,10 +14160,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14197,16 +14189,16 @@
         <v>188</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="M100" t="s" s="2">
+      <c r="N100" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="N100" t="s" s="2">
-        <v>440</v>
-      </c>
       <c r="O100" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>18</v>
@@ -14216,7 +14208,7 @@
         <v>18</v>
       </c>
       <c r="S100" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="T100" t="s" s="2">
         <v>18</v>
@@ -14231,14 +14223,14 @@
         <v>18</v>
       </c>
       <c r="X100" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="Y100" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="Y100" t="s" s="2">
+      <c r="Z100" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="Z100" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="AA100" t="s" s="2">
         <v>18</v>
       </c>
@@ -14255,7 +14247,7 @@
         <v>18</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>90</v>
@@ -14273,16 +14265,16 @@
         <v>18</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AM100" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AN100" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AN100" t="s" s="2">
+      <c r="AO100" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AO100" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>18</v>
@@ -14290,10 +14282,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14316,19 +14308,19 @@
         <v>91</v>
       </c>
       <c r="K101" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="L101" t="s" s="2">
         <v>564</v>
       </c>
-      <c r="L101" t="s" s="2">
-        <v>565</v>
-      </c>
       <c r="M101" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>18</v>
@@ -14377,7 +14369,7 @@
         <v>18</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -14395,27 +14387,27 @@
         <v>18</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AM101" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AN101" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AN101" t="s" s="2">
+      <c r="AO101" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP101" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AO101" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP101" t="s" s="2">
-        <v>284</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14441,16 +14433,16 @@
         <v>188</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="N102" t="s" s="2">
-        <v>450</v>
-      </c>
       <c r="O102" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>18</v>
@@ -14475,14 +14467,14 @@
         <v>18</v>
       </c>
       <c r="X102" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="Y102" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="Y102" t="s" s="2">
+      <c r="Z102" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="Z102" t="s" s="2">
-        <v>292</v>
-      </c>
       <c r="AA102" t="s" s="2">
         <v>18</v>
       </c>
@@ -14499,7 +14491,7 @@
         <v>18</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -14508,7 +14500,7 @@
         <v>90</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>102</v>
@@ -14523,7 +14515,7 @@
         <v>133</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>18</v>
@@ -14534,14 +14526,14 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
@@ -14563,16 +14555,16 @@
         <v>188</v>
       </c>
       <c r="L103" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M103" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="M103" t="s" s="2">
+      <c r="N103" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="N103" t="s" s="2">
+      <c r="O103" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>18</v>
@@ -14597,14 +14589,14 @@
         <v>18</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Y103" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="Z103" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="Z103" t="s" s="2">
-        <v>302</v>
-      </c>
       <c r="AA103" t="s" s="2">
         <v>18</v>
       </c>
@@ -14621,7 +14613,7 @@
         <v>18</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
@@ -14639,27 +14631,27 @@
         <v>18</v>
       </c>
       <c r="AL103" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AM103" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="AM103" t="s" s="2">
+      <c r="AN103" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="AN103" t="s" s="2">
+      <c r="AO103" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP103" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="AO103" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP103" t="s" s="2">
-        <v>306</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14685,16 +14677,16 @@
         <v>80</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="M104" t="s" s="2">
-        <v>454</v>
-      </c>
       <c r="N104" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="O104" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="O104" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>18</v>
@@ -14743,7 +14735,7 @@
         <v>18</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
@@ -14764,10 +14756,10 @@
         <v>18</v>
       </c>
       <c r="AM104" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AN104" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="AN104" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>18</v>

--- a/StructureDefinition-onc-abc-chart.xlsx
+++ b/StructureDefinition-onc-abc-chart.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T09:46:48+00:00</t>
+    <t>2026-07-11T14:02:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-abc-chart.xlsx
+++ b/StructureDefinition-onc-abc-chart.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T14:02:42+00:00</t>
+    <t>2026-07-11T14:17:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-abc-chart.xlsx
+++ b/StructureDefinition-onc-abc-chart.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T14:17:07+00:00</t>
+    <t>2026-07-11T14:32:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-abc-chart.xlsx
+++ b/StructureDefinition-onc-abc-chart.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T14:32:04+00:00</t>
+    <t>2026-07-11T14:47:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-abc-chart.xlsx
+++ b/StructureDefinition-onc-abc-chart.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T14:47:20+00:00</t>
+    <t>2026-07-11T18:02:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
